--- a/HikariWasabi-Grupo6-Backlog-Burndown v2.xlsx
+++ b/HikariWasabi-Grupo6-Backlog-Burndown v2.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04395b400f7f60cb/Desktop/Tecnologia da informação/Documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Desktop\Tecnologia da informação\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{D9A55B31-1194-4B75-9CAA-16CA1CF31086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0AC1443-F147-456B-A995-BE685DC8D095}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21AF9EB8-0062-47AF-B0EC-254FEB537C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{960F6042-E808-4157-B293-DF7D0877B487}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$2:$H$37</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="109">
   <si>
     <t>Pagina Site inicial</t>
   </si>
@@ -68,9 +71,6 @@
     <t>DashBoard</t>
   </si>
   <si>
-    <t>Pagina DashBoards</t>
-  </si>
-  <si>
     <t>Maquina virtual</t>
   </si>
   <si>
@@ -83,30 +83,9 @@
     <t>Grafico de Burndown</t>
   </si>
   <si>
-    <t>Pagina de Dashboard</t>
-  </si>
-  <si>
     <t>Conexão API VM</t>
   </si>
   <si>
-    <t>Pagina meus dados</t>
-  </si>
-  <si>
-    <t>Pagina safra wasabi</t>
-  </si>
-  <si>
-    <t>Conexão SITE + MySql</t>
-  </si>
-  <si>
-    <t>Pagina contato</t>
-  </si>
-  <si>
-    <t>Alerta Alta temperatura</t>
-  </si>
-  <si>
-    <t>Alerta de baixa humidade</t>
-  </si>
-  <si>
     <t>Requisito</t>
   </si>
   <si>
@@ -164,33 +143,9 @@
     <t>Criar o grafico de Burndown com base nos requisitos</t>
   </si>
   <si>
-    <t>Criar a pagina de DashBoards do site</t>
-  </si>
-  <si>
     <t>Conectar a  API com a VM</t>
   </si>
   <si>
-    <t xml:space="preserve">Conectar a API  com o site </t>
-  </si>
-  <si>
-    <t>Conexão Site  + API</t>
-  </si>
-  <si>
-    <t>Conectar o site com o banco de dados</t>
-  </si>
-  <si>
-    <t>Criar a pagina de contato do site</t>
-  </si>
-  <si>
-    <t>Criar a pagina dos dados do usuario do site</t>
-  </si>
-  <si>
-    <t>Criar a pagina sobre a safra do wasabi do cliente do site</t>
-  </si>
-  <si>
-    <t>Criar um alerta de alta temperatura no site</t>
-  </si>
-  <si>
     <t xml:space="preserve">Essencial </t>
   </si>
   <si>
@@ -278,15 +233,9 @@
     <t xml:space="preserve">Importante </t>
   </si>
   <si>
-    <t>Criar um alerta de baixa umidade no site</t>
-  </si>
-  <si>
     <t>Criar o diagrama de solução tecnica</t>
   </si>
   <si>
-    <t>Criar pagina apresentando as Dashboards do site</t>
-  </si>
-  <si>
     <t>Desenvolvimento</t>
   </si>
   <si>
@@ -299,9 +248,6 @@
     <t xml:space="preserve">SP3  </t>
   </si>
   <si>
-    <t>MÉDIA</t>
-  </si>
-  <si>
     <t>BACKLOG SPRINT 1</t>
   </si>
   <si>
@@ -326,21 +272,12 @@
     <t>Entregue</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
     <t>Total de Requisitos</t>
   </si>
   <si>
-    <t>Média</t>
-  </si>
-  <si>
     <t>Total pontos Fibonachi</t>
   </si>
   <si>
-    <t>BurnDown em andamento</t>
-  </si>
-  <si>
     <t>BurnDown Planejado</t>
   </si>
   <si>
@@ -351,13 +288,91 @@
   </si>
   <si>
     <t>BACKLOG HikariWasabi</t>
+  </si>
+  <si>
+    <t>Criar o diagrama de solução tecnicaCriar o diagrama de solução tecnicaCriar o diagrama de solução tecnica</t>
+  </si>
+  <si>
+    <t>Manual de Instalação</t>
+  </si>
+  <si>
+    <t>Doc Final do Projeto</t>
+  </si>
+  <si>
+    <t>Versão final site</t>
+  </si>
+  <si>
+    <t>Fluoxograma de Suporte</t>
+  </si>
+  <si>
+    <t>Ferramenta de Suporte</t>
+  </si>
+  <si>
+    <t>Versão final modeagem</t>
+  </si>
+  <si>
+    <t>Distribuir maquinas solução</t>
+  </si>
+  <si>
+    <t>Criar o manual de instalação do projeto</t>
+  </si>
+  <si>
+    <t>Validar e editar a documentação para uma versão final</t>
+  </si>
+  <si>
+    <t>Validar e editar o site para uma versão final</t>
+  </si>
+  <si>
+    <t>Criar o fluoxograma de suporte do site</t>
+  </si>
+  <si>
+    <t>Criar a ferramenta de suporte do site</t>
+  </si>
+  <si>
+    <t>Validar e editar a  modelagem do banco de dados</t>
+  </si>
+  <si>
+    <t>Conexão Api</t>
+  </si>
+  <si>
+    <t>Conexão safras</t>
+  </si>
+  <si>
+    <t>Conectar a API com as telas login, cadastro e contato inicial</t>
+  </si>
+  <si>
+    <t>Conectar a tela de safras junto com a criação de suas KPIS</t>
+  </si>
+  <si>
+    <t>Conexão DashBoard</t>
+  </si>
+  <si>
+    <t>Conectar a  API com a tela de DashBoard</t>
+  </si>
+  <si>
+    <t>Infraestrutra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desejavel </t>
+  </si>
+  <si>
+    <t>Essencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grande </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP3 </t>
+  </si>
+  <si>
+    <t>Distribuir as maquinas do projeto em 2 maquinas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,16 +401,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,12 +412,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,12 +441,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -468,14 +463,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -588,84 +577,141 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -700,36 +746,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Gráfico</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="pt-BR" baseline="0"/>
-              <a:t> de BurnDown HikariWasabi em andamento</a:t>
-            </a:r>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -768,9 +784,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>Entregue</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -785,7 +798,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Planilha1!$R$23:$R$26</c:f>
+              <c:f>Planilha1!$R$4:$R$7</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -805,75 +818,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$U$23:$U$26</c:f>
+              <c:f>Planilha1!$S$4:$S$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>84</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D7F2-433A-9659-2CD6B8A62805}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Planejado</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Planilha1!$R$23:$R$26</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>SP1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>SP2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>SP3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Planilha1!$T$23:$T$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>409</c:v>
+                  <c:v>393</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>100</c:v>
@@ -882,7 +832,7 @@
                   <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139</c:v>
+                  <c:v>123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -890,7 +840,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D7F2-433A-9659-2CD6B8A62805}"/>
+              <c16:uniqueId val="{00000000-6BE4-47FE-B327-05D181EF3968}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -903,11 +853,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="142695856"/>
-        <c:axId val="142680976"/>
+        <c:axId val="797395775"/>
+        <c:axId val="797393855"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="142695856"/>
+        <c:axId val="797395775"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -950,7 +900,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="142680976"/>
+        <c:crossAx val="797393855"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -958,7 +908,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="142680976"/>
+        <c:axId val="797393855"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -995,7 +945,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="142695856"/>
+        <c:crossAx val="797395775"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1007,37 +957,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1097,36 +1016,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Grafico</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="pt-BR" baseline="0"/>
-              <a:t> de BurnDown HikariWasabi Planejado</a:t>
-            </a:r>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1165,6 +1054,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Planejado</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -1179,7 +1071,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Planilha1!$R$23:$R$26</c:f>
+              <c:f>Planilha1!$R$15:$R$18</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1199,12 +1091,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$T$23:$T$26</c:f>
+              <c:f>Planilha1!$S$15:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>409</c:v>
+                  <c:v>393</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>100</c:v>
@@ -1213,7 +1105,7 @@
                   <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139</c:v>
+                  <c:v>123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1221,7 +1113,73 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-928C-432F-ACCB-102F9928283D}"/>
+              <c16:uniqueId val="{00000000-A1A4-4DEA-AAA6-C732DAD22EB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Entregue</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$R$15:$R$18</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SP3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$T$15:$T$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>393</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A1A4-4DEA-AAA6-C732DAD22EB8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1234,11 +1192,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="142656496"/>
-        <c:axId val="142666576"/>
+        <c:axId val="797307935"/>
+        <c:axId val="797298815"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="142656496"/>
+        <c:axId val="797307935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1281,7 +1239,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="142666576"/>
+        <c:crossAx val="797298815"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1289,12 +1247,26 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="142666576"/>
+        <c:axId val="797298815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1326,7 +1298,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="142656496"/>
+        <c:crossAx val="797307935"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1338,6 +1310,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2493,22 +2496,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>500742</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>128451</xdr:rowOff>
+      <xdr:colOff>410818</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>162340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>94705</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>516836</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>122583</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
+        <xdr:cNvPr id="4" name="Gráfico 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0416C588-BCD3-75BC-0282-E09979F5EFD7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A05D0A7-96A7-6EB9-6A7A-FCBF2F1A61F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2529,22 +2532,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>546975</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>52380</xdr:rowOff>
+      <xdr:colOff>510209</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>175591</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>51997</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>107256</xdr:rowOff>
+      <xdr:colOff>6627</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>135835</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
+        <xdr:cNvPr id="5" name="Gráfico 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{284FF7F6-BA17-56AE-3CC6-E1EC3A460224}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D2B750-D310-495C-E5D3-539B83E5CDF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2563,6 +2566,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2882,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}">
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:T87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.44140625" customWidth="1"/>
@@ -2893,2000 +2900,1987 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="36"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="18"/>
+      <c r="T2" s="19"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="27"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S4" s="3">
+        <v>393</v>
+      </c>
+      <c r="T4" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="27"/>
+      <c r="B5" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" s="3">
+        <v>100</v>
+      </c>
+      <c r="T5" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="27"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" s="3">
+        <v>170</v>
+      </c>
+      <c r="T6" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="27"/>
+      <c r="B7" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S7" s="3">
+        <v>123</v>
+      </c>
+      <c r="T7" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="27"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="27"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="27"/>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="27"/>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="27"/>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S13" s="18"/>
+      <c r="T13" s="19"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="27"/>
+      <c r="B14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R14" s="8"/>
+      <c r="S14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="T14" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="E15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S15" s="3">
+        <v>393</v>
+      </c>
+      <c r="T15" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+      <c r="B16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="2">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S16" s="3">
+        <v>100</v>
+      </c>
+      <c r="T16" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="27"/>
+      <c r="B17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2">
+        <v>21</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S17" s="3">
+        <v>170</v>
+      </c>
+      <c r="T17" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="3">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" s="3">
+        <v>123</v>
+      </c>
+      <c r="T18" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="28"/>
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="3">
+        <v>13</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="28"/>
+      <c r="B20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="3">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
+      <c r="B21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="3">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="28"/>
+      <c r="B22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A23" s="28"/>
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="3">
+        <v>21</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" s="28"/>
+      <c r="B24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="3">
+        <v>21</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" s="28"/>
+      <c r="B25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="3">
+        <v>13</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A26" s="28"/>
+      <c r="B26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="3">
+        <v>21</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A27" s="28"/>
+      <c r="B27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="3">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A28" s="28"/>
+      <c r="B28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="3">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A29" s="28"/>
+      <c r="B29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="3">
+        <v>13</v>
+      </c>
+      <c r="G29" s="3">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A30" s="28"/>
+      <c r="B30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="3">
+        <v>13</v>
+      </c>
+      <c r="G30" s="3">
+        <v>3</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A31" s="28"/>
+      <c r="B31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="3">
+        <v>21</v>
+      </c>
+      <c r="G31" s="3">
+        <v>3</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A32" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="4">
+        <v>5</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="29"/>
+      <c r="B33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="4">
+        <v>8</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="29"/>
+      <c r="B34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="4">
+        <v>8</v>
+      </c>
+      <c r="G34" s="4">
+        <v>3</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="29"/>
+      <c r="B35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="4">
+        <v>8</v>
+      </c>
+      <c r="G35" s="4">
+        <v>3</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="29"/>
+      <c r="B36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="4">
+        <v>13</v>
+      </c>
+      <c r="G36" s="4">
+        <v>3</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="29"/>
+      <c r="B37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="4">
+        <v>5</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L37" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="M37" s="39"/>
+      <c r="O37" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="P37" s="41"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L38" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M38" s="6">
+        <v>35</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P38" s="6">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M39" s="6">
+        <v>12</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P39" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L40" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M40" s="6">
+        <v>13</v>
+      </c>
+      <c r="O40" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="P40" s="16">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L41" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="M41" s="16">
+        <v>10</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P41" s="6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="25"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" s="2">
+        <v>5</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" s="30"/>
+      <c r="B48" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" s="2">
+        <v>8</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="30"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" s="2">
+        <v>8</v>
+      </c>
+      <c r="G49" s="2">
+        <v>3</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="30"/>
+      <c r="B50" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F50" s="2">
+        <v>3</v>
+      </c>
+      <c r="G50" s="2">
+        <v>2</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="30"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" s="2">
+        <v>8</v>
+      </c>
+      <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="30"/>
+      <c r="B52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F52" s="2">
+        <v>8</v>
+      </c>
+      <c r="G52" s="2">
+        <v>2</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="30"/>
+      <c r="B53" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F53" s="2">
+        <v>8</v>
+      </c>
+      <c r="G53" s="2">
+        <v>3</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="3">
+        <v>13</v>
+      </c>
+      <c r="G54" s="3">
+        <v>2</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="13"/>
+      <c r="B55" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" s="3">
+        <v>13</v>
+      </c>
+      <c r="G55" s="3">
+        <v>2</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="15"/>
+      <c r="B56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F56" s="3">
+        <v>13</v>
+      </c>
+      <c r="G56" s="3">
+        <v>3</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" s="4">
+        <v>8</v>
+      </c>
+      <c r="G57" s="4">
+        <v>3</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="25"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F63" s="2">
+        <v>5</v>
+      </c>
+      <c r="G63" s="2">
+        <v>2</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="33"/>
+      <c r="B64" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="2">
+        <v>8</v>
+      </c>
+      <c r="G64" s="2">
+        <v>2</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="33"/>
+      <c r="B65" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F65" s="2">
+        <v>13</v>
+      </c>
+      <c r="G65" s="2">
+        <v>3</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="34"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F66" s="2">
+        <v>21</v>
+      </c>
+      <c r="G66" s="2">
+        <v>3</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" s="3">
+        <v>13</v>
+      </c>
+      <c r="G67" s="3">
+        <v>2</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="28"/>
+      <c r="B68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F68" s="3">
+        <v>13</v>
+      </c>
+      <c r="G68" s="3">
+        <v>3</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="28"/>
+      <c r="B69" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F69" s="3">
+        <v>21</v>
+      </c>
+      <c r="G69" s="3">
+        <v>3</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="28"/>
+      <c r="B70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D70" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F70" s="3">
+        <v>21</v>
+      </c>
+      <c r="G70" s="3">
+        <v>3</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="28"/>
+      <c r="B71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F71" s="3">
+        <v>21</v>
+      </c>
+      <c r="G71" s="3">
+        <v>3</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="B72" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F72" s="4">
+        <v>5</v>
+      </c>
+      <c r="G72" s="4">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="29"/>
+      <c r="B73" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F73" s="4">
         <v>8</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G73" s="4">
         <v>2</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" s="9"/>
-      <c r="S3" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="32"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="H73" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N73" s="9"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="29"/>
+      <c r="B74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="F74" s="4">
         <v>8</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G74" s="4">
         <v>3</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="S4" s="4">
-        <v>409</v>
-      </c>
-      <c r="T4" s="3">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="32"/>
-      <c r="B5" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="3">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3">
-        <v>2</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="S5" s="4">
-        <v>100</v>
-      </c>
-      <c r="T5" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="3">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3">
-        <v>2</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="S6" s="4">
-        <v>170</v>
-      </c>
-      <c r="T6" s="3">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
-      <c r="B7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="3">
-        <v>21</v>
-      </c>
-      <c r="G7" s="3">
-        <v>3</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="S7" s="4">
-        <v>139</v>
-      </c>
-      <c r="T7" s="3">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="3" t="s">
+      <c r="H74" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="29"/>
+      <c r="B75" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="3">
-        <v>13</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="3">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="3">
-        <v>5</v>
-      </c>
-      <c r="G11" s="3">
-        <v>2</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
-      <c r="B12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="3">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="3">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3">
-        <v>3</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="4">
-        <v>13</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="4">
-        <v>13</v>
-      </c>
-      <c r="G15" s="4">
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
-      <c r="B16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="4">
-        <v>13</v>
-      </c>
-      <c r="G16" s="4">
-        <v>3</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
-      <c r="B17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="4">
-        <v>21</v>
-      </c>
-      <c r="G17" s="4">
-        <v>2</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
-      <c r="B18" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="4">
-        <v>13</v>
-      </c>
-      <c r="G18" s="4">
-        <v>2</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
-      <c r="B19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="4">
-        <v>5</v>
-      </c>
-      <c r="G19" s="4">
-        <v>3</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
-      <c r="B20" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="4">
-        <v>21</v>
-      </c>
-      <c r="G20" s="4">
-        <v>3</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="4">
-        <v>21</v>
-      </c>
-      <c r="G21" s="4">
-        <v>2</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R21" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
-      <c r="B22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="4">
-        <v>21</v>
-      </c>
-      <c r="G22" s="4">
-        <v>3</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="T22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="V22" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A23" s="20"/>
-      <c r="B23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F23" s="4">
-        <v>8</v>
-      </c>
-      <c r="G23" s="4">
-        <v>2</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R23" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="S23" s="4">
-        <v>409</v>
-      </c>
-      <c r="T23" s="3">
-        <v>409</v>
-      </c>
-      <c r="U23" s="3">
-        <v>18</v>
-      </c>
-      <c r="V23" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A24" s="20"/>
-      <c r="B24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="4">
-        <v>13</v>
-      </c>
-      <c r="G24" s="4">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="S24" s="4">
-        <v>100</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
-      <c r="B25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="4">
-        <v>8</v>
-      </c>
-      <c r="G25" s="4">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R25" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="S25" s="4">
-        <v>170</v>
-      </c>
-      <c r="T25" s="3">
-        <v>170</v>
-      </c>
-      <c r="U25" s="3">
-        <v>84</v>
-      </c>
-      <c r="V25" s="3">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A26" s="20"/>
-      <c r="B26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" s="4">
-        <v>21</v>
-      </c>
-      <c r="G26" s="4">
-        <v>3</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="S26" s="4">
-        <v>139</v>
-      </c>
-      <c r="T26" s="3">
-        <v>139</v>
-      </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A27" s="20"/>
-      <c r="B27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="4">
-        <v>21</v>
-      </c>
-      <c r="G27" s="4">
-        <v>3</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
-      <c r="B28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="4">
-        <v>13</v>
-      </c>
-      <c r="G28" s="4">
-        <v>2</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A29" s="20"/>
-      <c r="B29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F29" s="4">
-        <v>13</v>
-      </c>
-      <c r="G29" s="4">
-        <v>2</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A30" s="20"/>
-      <c r="B30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F30" s="4">
-        <v>13</v>
-      </c>
-      <c r="G30" s="4">
-        <v>3</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A31" s="20"/>
-      <c r="B31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F31" s="4">
-        <v>21</v>
-      </c>
-      <c r="G31" s="4">
-        <v>3</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F32" s="5">
-        <v>5</v>
-      </c>
-      <c r="G32" s="5">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="25"/>
-      <c r="B33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="5">
-        <v>8</v>
-      </c>
-      <c r="G33" s="5">
-        <v>2</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="25"/>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="5">
-        <v>8</v>
-      </c>
-      <c r="G34" s="5">
-        <v>3</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="25"/>
-      <c r="B35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F35" s="5">
-        <v>8</v>
-      </c>
-      <c r="G35" s="5">
-        <v>3</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="25"/>
-      <c r="B36" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F36" s="5">
-        <v>13</v>
-      </c>
-      <c r="G36" s="5">
-        <v>3</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="J38" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="M38" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="N38" s="16"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="J39" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K39" s="7">
-        <v>34</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="N39" s="7">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K40" s="7">
-        <v>12</v>
-      </c>
-      <c r="M40" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N40" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F41" s="3">
-        <v>5</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="K41" s="7">
-        <v>13</v>
-      </c>
-      <c r="M41" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="N41" s="7">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="23"/>
-      <c r="B42" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F42" s="3">
-        <v>8</v>
-      </c>
-      <c r="G42" s="3">
-        <v>2</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="K42" s="7">
-        <v>9</v>
-      </c>
-      <c r="M42" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="N42" s="7">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="23"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" s="3">
-        <v>8</v>
-      </c>
-      <c r="G43" s="3">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="K43" s="7">
-        <v>11.33</v>
-      </c>
-      <c r="M43" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="N43" s="7">
-        <v>136.333</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="23"/>
-      <c r="B44" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F44" s="3">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3">
-        <v>2</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="23"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F45" s="3">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="23"/>
-      <c r="B46" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="3">
-        <v>8</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="23"/>
-      <c r="B47" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F47" s="3">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F48" s="4">
-        <v>5</v>
-      </c>
-      <c r="G48" s="4">
-        <v>3</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="18"/>
-      <c r="B49" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F49" s="4">
-        <v>13</v>
-      </c>
-      <c r="G49" s="4">
-        <v>2</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="18"/>
-      <c r="B50" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F50" s="4">
-        <v>13</v>
-      </c>
-      <c r="G50" s="4">
-        <v>2</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="18"/>
-      <c r="B51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F51" s="4">
-        <v>13</v>
-      </c>
-      <c r="G51" s="4">
-        <v>3</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F52" s="5">
-        <v>8</v>
-      </c>
-      <c r="G52" s="5">
-        <v>3</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C53" s="14"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F56" s="3">
-        <v>5</v>
-      </c>
-      <c r="G56" s="3">
-        <v>2</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="29"/>
-      <c r="B57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F57" s="3">
-        <v>8</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="29"/>
-      <c r="B58" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F58" s="3">
-        <v>13</v>
-      </c>
-      <c r="G58" s="3">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="30"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F59" s="3">
-        <v>21</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F60" s="4">
-        <v>13</v>
-      </c>
-      <c r="G60" s="4">
-        <v>2</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="20"/>
-      <c r="B61" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F61" s="4">
-        <v>13</v>
-      </c>
-      <c r="G61" s="4">
-        <v>3</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="20"/>
-      <c r="B62" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F62" s="4">
-        <v>21</v>
-      </c>
-      <c r="G62" s="4">
-        <v>3</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="20"/>
-      <c r="B63" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F63" s="4">
-        <v>21</v>
-      </c>
-      <c r="G63" s="4">
-        <v>3</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="20"/>
-      <c r="B64" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F64" s="4">
-        <v>21</v>
-      </c>
-      <c r="G64" s="4">
-        <v>3</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F65" s="5">
-        <v>5</v>
-      </c>
-      <c r="G65" s="5">
-        <v>1</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="21"/>
-      <c r="B66" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F66" s="5">
-        <v>8</v>
-      </c>
-      <c r="G66" s="5">
-        <v>2</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="21"/>
-      <c r="B67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F67" s="5">
-        <v>8</v>
-      </c>
-      <c r="G67" s="5">
-        <v>3</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="21"/>
-      <c r="B68" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F68" s="5">
-        <v>13</v>
-      </c>
-      <c r="G68" s="5">
-        <v>3</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F71" s="4">
-        <v>8</v>
-      </c>
-      <c r="G71" s="4">
-        <v>1</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="18"/>
-      <c r="B72" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F72" s="4">
-        <v>8</v>
-      </c>
-      <c r="G72" s="4">
-        <v>2</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="18"/>
-      <c r="B73" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F73" s="4">
-        <v>13</v>
-      </c>
-      <c r="G73" s="4">
-        <v>1</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="18"/>
-      <c r="B74" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F74" s="4">
-        <v>13</v>
-      </c>
-      <c r="G74" s="4">
-        <v>2</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="18"/>
-      <c r="B75" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="F75" s="4">
         <v>13</v>
       </c>
       <c r="G75" s="4">
+        <v>3</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F78" s="2">
+        <v>8</v>
+      </c>
+      <c r="G78" s="2">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="30"/>
+      <c r="B79" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F79" s="2">
+        <v>8</v>
+      </c>
+      <c r="G79" s="2">
+        <v>1</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="30"/>
+      <c r="B80" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F80" s="2">
+        <v>13</v>
+      </c>
+      <c r="G80" s="2">
         <v>2</v>
       </c>
-      <c r="H75" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="18"/>
-      <c r="B76" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="H80" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="30"/>
+      <c r="B81" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F81" s="2">
+        <v>21</v>
+      </c>
+      <c r="G81" s="2">
+        <v>2</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F82" s="3">
+        <v>13</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="21"/>
+      <c r="B83" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F83" s="3">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="21"/>
+      <c r="B84" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F84" s="3">
+        <v>13</v>
+      </c>
+      <c r="G84" s="3">
+        <v>3</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="21"/>
+      <c r="B85" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F85" s="3">
+        <v>13</v>
+      </c>
+      <c r="G85" s="3">
+        <v>3</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="22"/>
+      <c r="B86" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F86" s="3">
+        <v>21</v>
+      </c>
+      <c r="G86" s="3">
+        <v>3</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F76" s="4">
-        <v>21</v>
-      </c>
-      <c r="G76" s="4">
-        <v>2</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="18"/>
-      <c r="B77" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F77" s="4">
-        <v>21</v>
-      </c>
-      <c r="G77" s="4">
-        <v>2</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="18"/>
-      <c r="B78" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C78" s="4" t="s">
+      <c r="F87" s="4">
+        <v>5</v>
+      </c>
+      <c r="G87" s="4">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F78" s="4">
-        <v>21</v>
-      </c>
-      <c r="G78" s="4">
-        <v>3</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="18"/>
-      <c r="B79" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F79" s="4">
-        <v>21</v>
-      </c>
-      <c r="G79" s="4">
-        <v>3</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="96" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N96" s="11"/>
-    </row>
-    <row r="98" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <autoFilter ref="A2:H37" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}"/>
+  <mergeCells count="22">
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="A47:A53"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="O37:P37"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A3:A13"/>
+    <mergeCell ref="A77:H77"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="R21:V21"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="A71:A79"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A14:A31"/>
-    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A3:A17"/>
+    <mergeCell ref="A18:A31"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="L37:M37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/HikariWasabi-Grupo6-Backlog-Burndown v2.xlsx
+++ b/HikariWasabi-Grupo6-Backlog-Burndown v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Desktop\Tecnologia da informação\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21AF9EB8-0062-47AF-B0EC-254FEB537C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E823EDCD-355E-4ABF-956A-1474B78FC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{960F6042-E808-4157-B293-DF7D0877B487}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{960F6042-E808-4157-B293-DF7D0877B487}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -799,42 +799,11 @@
           <c:cat>
             <c:strRef>
               <c:f>Planilha1!$R$4:$R$7</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>SP1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>SP2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>SP3</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Planilha1!$S$4:$S$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>393</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>170</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>123</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -852,6 +821,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="797395775"/>
         <c:axId val="797393855"/>
@@ -1073,7 +1043,7 @@
             <c:strRef>
               <c:f>Planilha1!$R$15:$R$18</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>Total</c:v>
                 </c:pt>
@@ -1083,9 +1053,6 @@
                 <c:pt idx="2">
                   <c:v>SP2</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>SP3</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -1094,7 +1061,7 @@
               <c:f>Planilha1!$S$15:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>393</c:v>
                 </c:pt>
@@ -1103,9 +1070,6 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>170</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1139,7 +1103,7 @@
             <c:strRef>
               <c:f>Planilha1!$R$15:$R$18</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>Total</c:v>
                 </c:pt>
@@ -1149,9 +1113,6 @@
                 <c:pt idx="2">
                   <c:v>SP2</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>SP3</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -1160,7 +1121,7 @@
               <c:f>Planilha1!$T$15:$T$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>393</c:v>
                 </c:pt>
@@ -1169,9 +1130,6 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>170</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2889,6 +2847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:T87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2942,7 +2901,7 @@
       <c r="S2" s="18"/>
       <c r="T2" s="19"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>53</v>
       </c>
@@ -2975,7 +2934,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="38"/>
       <c r="C4" s="2" t="s">
@@ -3006,7 +2965,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="27"/>
       <c r="B5" s="38" t="s">
         <v>47</v>
@@ -3039,7 +2998,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="27"/>
       <c r="B6" s="38"/>
       <c r="C6" s="2" t="s">
@@ -3070,7 +3029,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27"/>
       <c r="B7" s="38" t="s">
         <v>9</v>
@@ -3103,7 +3062,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27"/>
       <c r="B8" s="38"/>
       <c r="C8" s="2" t="s">
@@ -3125,7 +3084,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27"/>
       <c r="B9" s="38"/>
       <c r="C9" s="2" t="s">
@@ -3147,7 +3106,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="27"/>
       <c r="B10" s="2" t="s">
         <v>13</v>
@@ -3171,7 +3130,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="27"/>
       <c r="B11" s="2" t="s">
         <v>8</v>
@@ -3195,7 +3154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27"/>
       <c r="B12" s="2" t="s">
         <v>47</v>
@@ -3219,7 +3178,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27"/>
       <c r="B13" s="2" t="s">
         <v>58</v>
@@ -3378,7 +3337,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>65</v>
       </c>
@@ -3413,7 +3372,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="28"/>
       <c r="B19" s="3" t="s">
         <v>1</v>
@@ -3437,7 +3396,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="28"/>
       <c r="B20" s="3" t="s">
         <v>2</v>
@@ -3461,7 +3420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="28"/>
       <c r="B21" s="3" t="s">
         <v>3</v>
@@ -3485,7 +3444,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="28"/>
       <c r="B22" s="3" t="s">
         <v>4</v>
@@ -3509,7 +3468,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="28"/>
       <c r="B23" s="3" t="s">
         <v>5</v>
@@ -3533,7 +3492,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="28"/>
       <c r="B24" s="3" t="s">
         <v>6</v>
@@ -3557,7 +3516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="28"/>
       <c r="B25" s="3" t="s">
         <v>7</v>
@@ -3581,7 +3540,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="28"/>
       <c r="B26" s="3" t="s">
         <v>45</v>
@@ -3725,7 +3684,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
         <v>54</v>
       </c>
@@ -3751,7 +3710,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="29"/>
       <c r="B33" s="4" t="s">
         <v>29</v>
@@ -3775,7 +3734,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29"/>
       <c r="B34" s="4" t="s">
         <v>10</v>
@@ -3799,7 +3758,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="29"/>
       <c r="B35" s="4" t="s">
         <v>11</v>
@@ -3823,7 +3782,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="29"/>
       <c r="B36" s="4" t="s">
         <v>14</v>
@@ -4853,7 +4812,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H37" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}"/>
+  <autoFilter ref="A2:H37" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="SP3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="22">
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="A47:A53"/>

--- a/HikariWasabi-Grupo6-Backlog-Burndown v2.xlsx
+++ b/HikariWasabi-Grupo6-Backlog-Burndown v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Desktop\Tecnologia da informação\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04395b400f7f60cb/Desktop/Tecnologia da informação/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E823EDCD-355E-4ABF-956A-1474B78FC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{E823EDCD-355E-4ABF-956A-1474B78FC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0FB7E4-33E3-498C-A336-E78EFAC7C019}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{960F6042-E808-4157-B293-DF7D0877B487}"/>
+    <workbookView minimized="1" xWindow="5256" yWindow="2628" windowWidth="17280" windowHeight="8880" xr2:uid="{960F6042-E808-4157-B293-DF7D0877B487}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -639,15 +639,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -705,7 +696,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -713,6 +710,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -799,11 +799,42 @@
           <c:cat>
             <c:strRef>
               <c:f>Planilha1!$R$4:$R$7</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SP3</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Planilha1!$S$4:$S$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>393</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>123</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -821,7 +852,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="797395775"/>
         <c:axId val="797393855"/>
@@ -1043,7 +1073,7 @@
             <c:strRef>
               <c:f>Planilha1!$R$15:$R$18</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Total</c:v>
                 </c:pt>
@@ -1053,6 +1083,9 @@
                 <c:pt idx="2">
                   <c:v>SP2</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>SP3</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -1061,7 +1094,7 @@
               <c:f>Planilha1!$S$15:$S$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>393</c:v>
                 </c:pt>
@@ -1070,6 +1103,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1103,7 +1139,7 @@
             <c:strRef>
               <c:f>Planilha1!$R$15:$R$18</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Total</c:v>
                 </c:pt>
@@ -1113,6 +1149,9 @@
                 <c:pt idx="2">
                   <c:v>SP2</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>SP3</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -1121,7 +1160,7 @@
               <c:f>Planilha1!$T$15:$T$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>393</c:v>
                 </c:pt>
@@ -1130,6 +1169,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2847,7 +2889,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2859,16 +2900,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -2895,17 +2936,17 @@
       <c r="H2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="R2" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="18"/>
-      <c r="T2" s="19"/>
-    </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="S2" s="37"/>
+      <c r="T2" s="38"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="35" t="s">
         <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2934,9 +2975,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
-      <c r="B4" s="38"/>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="24"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="2" t="s">
         <v>57</v>
       </c>
@@ -2965,9 +3006,9 @@
         <v>393</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="B5" s="38" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="24"/>
+      <c r="B5" s="35" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2998,9 +3039,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="38"/>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="24"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="2" t="s">
         <v>59</v>
       </c>
@@ -3029,9 +3070,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
-      <c r="B7" s="38" t="s">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="24"/>
+      <c r="B7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3062,9 +3103,9 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="38"/>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="24"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="2" t="s">
         <v>27</v>
       </c>
@@ -3084,9 +3125,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="38"/>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="24"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
@@ -3106,8 +3147,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="24"/>
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
@@ -3130,8 +3171,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="24"/>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
@@ -3154,8 +3195,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="24"/>
       <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
@@ -3178,8 +3219,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="24"/>
       <c r="B13" s="2" t="s">
         <v>58</v>
       </c>
@@ -3201,14 +3242,14 @@
       <c r="H13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R13" s="17" t="s">
+      <c r="R13" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="S13" s="18"/>
-      <c r="T13" s="19"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="38"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="2" t="s">
         <v>84</v>
       </c>
@@ -3239,7 +3280,7 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="2" t="s">
         <v>85</v>
       </c>
@@ -3272,7 +3313,7 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="2" t="s">
         <v>87</v>
       </c>
@@ -3305,7 +3346,7 @@
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="2" t="s">
         <v>88</v>
       </c>
@@ -3337,8 +3378,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -3369,11 +3410,11 @@
         <v>123</v>
       </c>
       <c r="T18" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="25"/>
       <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
@@ -3396,8 +3437,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="25"/>
       <c r="B20" s="3" t="s">
         <v>2</v>
       </c>
@@ -3420,8 +3461,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="25"/>
       <c r="B21" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3485,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="25"/>
       <c r="B22" s="3" t="s">
         <v>4</v>
       </c>
@@ -3468,8 +3509,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A23" s="25"/>
       <c r="B23" s="3" t="s">
         <v>5</v>
       </c>
@@ -3492,8 +3533,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" s="25"/>
       <c r="B24" s="3" t="s">
         <v>6</v>
       </c>
@@ -3516,8 +3557,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" s="25"/>
       <c r="B25" s="3" t="s">
         <v>7</v>
       </c>
@@ -3540,8 +3581,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A26" s="25"/>
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
@@ -3565,7 +3606,7 @@
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="3" t="s">
         <v>86</v>
       </c>
@@ -3589,7 +3630,7 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="3" t="s">
         <v>89</v>
       </c>
@@ -3613,7 +3654,7 @@
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="3" t="s">
         <v>97</v>
       </c>
@@ -3637,7 +3678,7 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="3" t="s">
         <v>98</v>
       </c>
@@ -3661,7 +3702,7 @@
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="3" t="s">
         <v>101</v>
       </c>
@@ -3684,8 +3725,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="29" t="s">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A32" s="26" t="s">
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -3710,8 +3751,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="29"/>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="26"/>
       <c r="B33" s="4" t="s">
         <v>29</v>
       </c>
@@ -3734,8 +3775,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="29"/>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="26"/>
       <c r="B34" s="4" t="s">
         <v>10</v>
       </c>
@@ -3758,8 +3799,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="29"/>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="26"/>
       <c r="B35" s="4" t="s">
         <v>11</v>
       </c>
@@ -3782,8 +3823,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="29"/>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="26"/>
       <c r="B36" s="4" t="s">
         <v>14</v>
       </c>
@@ -3807,7 +3848,7 @@
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="29"/>
+      <c r="A37" s="26"/>
       <c r="B37" s="4" t="s">
         <v>90</v>
       </c>
@@ -3829,14 +3870,14 @@
       <c r="H37" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="L37" s="39" t="s">
+      <c r="L37" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="M37" s="39"/>
-      <c r="O37" s="40" t="s">
+      <c r="M37" s="41"/>
+      <c r="O37" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="P37" s="41"/>
+      <c r="P37" s="40"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L38" s="6" t="s">
@@ -3895,16 +3936,16 @@
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="25"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="22"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -3933,7 +3974,7 @@
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="27" t="s">
         <v>71</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -3959,8 +4000,8 @@
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" s="30"/>
-      <c r="B48" s="38" t="s">
+      <c r="A48" s="27"/>
+      <c r="B48" s="35" t="s">
         <v>55</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -3983,8 +4024,8 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="30"/>
-      <c r="B49" s="38"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="2" t="s">
         <v>57</v>
       </c>
@@ -4005,8 +4046,8 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="30"/>
-      <c r="B50" s="38" t="s">
+      <c r="A50" s="27"/>
+      <c r="B50" s="35" t="s">
         <v>47</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -4029,8 +4070,8 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="30"/>
-      <c r="B51" s="38"/>
+      <c r="A51" s="27"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="2" t="s">
         <v>59</v>
       </c>
@@ -4051,7 +4092,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="30"/>
+      <c r="A52" s="27"/>
       <c r="B52" s="2" t="s">
         <v>47</v>
       </c>
@@ -4075,7 +4116,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="30"/>
+      <c r="A53" s="27"/>
       <c r="B53" s="2" t="s">
         <v>58</v>
       </c>
@@ -4199,16 +4240,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="25"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="22"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
@@ -4237,7 +4278,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="32" t="s">
+      <c r="A63" s="29" t="s">
         <v>71</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -4263,7 +4304,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
+      <c r="A64" s="30"/>
       <c r="B64" s="2" t="s">
         <v>13</v>
       </c>
@@ -4287,7 +4328,7 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
+      <c r="A65" s="30"/>
       <c r="B65" s="14" t="s">
         <v>9</v>
       </c>
@@ -4311,7 +4352,7 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="34"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="14"/>
       <c r="C66" s="2" t="s">
         <v>80</v>
@@ -4333,7 +4374,7 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="31" t="s">
+      <c r="A67" s="28" t="s">
         <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -4359,7 +4400,7 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="28"/>
+      <c r="A68" s="25"/>
       <c r="B68" s="3" t="s">
         <v>2</v>
       </c>
@@ -4383,7 +4424,7 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="28"/>
+      <c r="A69" s="25"/>
       <c r="B69" s="3" t="s">
         <v>5</v>
       </c>
@@ -4407,7 +4448,7 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="28"/>
+      <c r="A70" s="25"/>
       <c r="B70" s="3" t="s">
         <v>6</v>
       </c>
@@ -4431,7 +4472,7 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="28"/>
+      <c r="A71" s="25"/>
       <c r="B71" s="3" t="s">
         <v>45</v>
       </c>
@@ -4455,7 +4496,7 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="26" t="s">
         <v>54</v>
       </c>
       <c r="B72" s="4" t="s">
@@ -4481,7 +4522,7 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="29"/>
+      <c r="A73" s="26"/>
       <c r="B73" s="4" t="s">
         <v>29</v>
       </c>
@@ -4506,7 +4547,7 @@
       <c r="N73" s="9"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="29"/>
+      <c r="A74" s="26"/>
       <c r="B74" s="4" t="s">
         <v>11</v>
       </c>
@@ -4530,7 +4571,7 @@
       </c>
     </row>
     <row r="75" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="29"/>
+      <c r="A75" s="26"/>
       <c r="B75" s="4" t="s">
         <v>14</v>
       </c>
@@ -4554,19 +4595,19 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="37" t="s">
+      <c r="A77" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="37"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="34"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="34"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="30" t="s">
+      <c r="A78" s="27" t="s">
         <v>71</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -4592,7 +4633,7 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="30"/>
+      <c r="A79" s="27"/>
       <c r="B79" s="2" t="s">
         <v>85</v>
       </c>
@@ -4616,7 +4657,7 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="30"/>
+      <c r="A80" s="27"/>
       <c r="B80" s="2" t="s">
         <v>87</v>
       </c>
@@ -4640,7 +4681,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="30"/>
+      <c r="A81" s="27"/>
       <c r="B81" s="2" t="s">
         <v>88</v>
       </c>
@@ -4664,7 +4705,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -4690,7 +4731,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="21"/>
+      <c r="A83" s="18"/>
       <c r="B83" s="3" t="s">
         <v>89</v>
       </c>
@@ -4714,7 +4755,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="21"/>
+      <c r="A84" s="18"/>
       <c r="B84" s="3" t="s">
         <v>97</v>
       </c>
@@ -4738,7 +4779,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="21"/>
+      <c r="A85" s="18"/>
       <c r="B85" s="3" t="s">
         <v>98</v>
       </c>
@@ -4762,7 +4803,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="22"/>
+      <c r="A86" s="19"/>
       <c r="B86" s="3" t="s">
         <v>101</v>
       </c>
@@ -4812,25 +4853,20 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H37" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="SP3"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:H37" xr:uid="{84DDDEBA-3FFC-4EB0-8A5E-4BC758C8A03B}"/>
   <mergeCells count="22">
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="A47:A53"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="O37:P37"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="L37:M37"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A77:H77"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B9"/>
-    <mergeCell ref="R13:T13"/>
     <mergeCell ref="A82:A86"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A3:A17"/>
@@ -4841,7 +4877,6 @@
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A63:A66"/>
     <mergeCell ref="A72:A75"/>
-    <mergeCell ref="L37:M37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
